--- a/output/Foreign_Assets_Schedule_FA_Rajani_Sanjeev_Joint_AY2026-27.xlsx
+++ b/output/Foreign_Assets_Schedule_FA_Rajani_Sanjeev_Joint_AY2026-27.xlsx
@@ -2548,7 +2548,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Account: IBKR U21864112 — Rajani J Vallath and Sanjeev K Nair (Individual, USD base, Cash).</t>
+          <t>Account: IBKR U21864112 — Rajani J Vallath and Sanjeev K Nair (Joint, USD base, Cash).</t>
         </is>
       </c>
     </row>
